--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/11,08,26 Останкино СЫРЫ/дв 11,08,26 бррсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/11,08,26 Останкино СЫРЫ/дв 11,08,26 бррсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\11,08,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979333D6-6D44-4E49-98B7-5E8971BA4116}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC1F6ED-9D39-4D19-81A6-B6A8C443EEAD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="103">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -356,6 +356,9 @@
   <si>
     <t>17,08,</t>
   </si>
+  <si>
+    <t>13,08,26 - отсутствует на заводе</t>
+  </si>
 </sst>
 </file>
 
@@ -407,7 +410,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -448,6 +451,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -484,7 +493,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -504,6 +513,8 @@
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1169,7 +1180,7 @@
       </c>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
-        <v>1681</v>
+        <v>1501</v>
       </c>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
@@ -1808,9 +1819,8 @@
         <f>14*P11-O11-F11</f>
         <v>180.59999999999997</v>
       </c>
-      <c r="R11" s="5">
-        <f>VLOOKUP(A11,заказ!A:B,2,0)</f>
-        <v>180</v>
+      <c r="R11" s="19">
+        <v>0</v>
       </c>
       <c r="S11" s="1">
         <f t="shared" si="4"/>
@@ -1850,7 +1860,9 @@
       <c r="AD11" s="1">
         <v>5.6</v>
       </c>
-      <c r="AE11" s="1"/>
+      <c r="AE11" s="20" t="s">
+        <v>102</v>
+      </c>
       <c r="AF11" s="1">
         <f t="shared" si="6"/>
         <v>32.507999999999996</v>
